--- a/artfynd/A 13961-2026 artfynd.xlsx
+++ b/artfynd/A 13961-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110599532</v>
+        <v>112681068</v>
       </c>
       <c r="B2" t="n">
-        <v>95538</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kanalberget (Kanalberget), Dlr</t>
+          <t>Kanalberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533123.1428080841</v>
+        <v>532936</v>
       </c>
       <c r="R2" t="n">
-        <v>6748734.190604645</v>
+        <v>6748863</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:09</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:09</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,85 +754,66 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110599642</v>
+        <v>112681079</v>
       </c>
       <c r="B3" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kanalberget (Kanalberget), Dlr</t>
+          <t>Kanalberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533130.8523702191</v>
+        <v>533171</v>
       </c>
       <c r="R3" t="n">
-        <v>6748744.490522006</v>
+        <v>6748787</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,22 +851,681 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112681077</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kanalberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>533171</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6748787</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112681082</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kanalberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>533191</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6748780</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110596930</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kanalberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>533110</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6748730</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Utspridda i hela området i norrsluttning av Kanalberget</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Göran Ehn</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Göran Ehn</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>109880953</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kanalberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>533110</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6748730</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>110599642</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kanalberget, Kanalberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>533131</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6748744</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>110599532</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kanalberget, Kanalberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>533123</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6748734</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13961-2026 artfynd.xlsx
+++ b/artfynd/A 13961-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112681068</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112681079</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112681077</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112681082</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110596930</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109880953</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110599642</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1526,8 +1566,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110599532</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>